--- a/data/trans_dic/P19C06-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C06-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por tratamiento de las enfermedades de las encías</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por tratamiento de las enfermedades de las encías (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,7</t>
+          <t>0,0; 3,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,14</t>
+          <t>0,7; 4,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,13</t>
+          <t>1,11; 5,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 8,85</t>
+          <t>0,25; 8,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,95</t>
+          <t>1,72; 6,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,93</t>
+          <t>0,38; 4,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,5</t>
+          <t>0,17; 1,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,1</t>
+          <t>0,24; 2,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,5</t>
+          <t>1,65; 4,59</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,64</t>
+          <t>0,99; 3,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,38</t>
+          <t>0,43; 3,93</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,43</t>
+          <t>0,51; 3,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,32</t>
+          <t>0,24; 2,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,87</t>
+          <t>0,64; 2,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,05</t>
+          <t>0,23; 1,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,87</t>
+          <t>0,27; 1,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,37</t>
+          <t>0,72; 2,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,62</t>
+          <t>0,27; 1,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,35</t>
+          <t>0,26; 1,32</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,72</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,04</t>
+          <t>0,34; 3,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,35</t>
+          <t>0,4; 3,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,58</t>
+          <t>1,45; 6,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,54</t>
+          <t>0,64; 2,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,63</t>
+          <t>0,18; 1,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,93</t>
+          <t>1,2; 3,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,33</t>
+          <t>0,67; 2,3</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,98</t>
+          <t>0,35; 3,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,11</t>
+          <t>0,0; 4,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,65</t>
+          <t>0,18; 2,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,26</t>
+          <t>0,93; 4,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,38</t>
+          <t>0,26; 2,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,67</t>
+          <t>0,58; 3,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,48</t>
+          <t>0,26; 2,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,17</t>
+          <t>0,88; 3,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,44</t>
+          <t>0,3; 2,39</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,83</t>
+          <t>0,29; 1,77</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,04</t>
+          <t>0,39; 1,87</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,88</t>
+          <t>0,57; 5,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 3,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,25</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,6</t>
+          <t>0,56; 4,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,1</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,42</t>
+          <t>0,55; 3,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,59</t>
+          <t>0,31; 2,59</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,51</t>
+          <t>0,38; 3,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,85</t>
+          <t>0,42; 5,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,14</t>
+          <t>0,6; 3,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,72</t>
+          <t>0,39; 3,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,48</t>
+          <t>0,43; 2,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,65</t>
+          <t>0,58; 2,7</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,58</t>
+          <t>0,4; 2,46</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,88</t>
+          <t>0,72; 2,77</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,23</t>
+          <t>0,2; 2,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,35</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,63</t>
+          <t>0,24; 3,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,87</t>
+          <t>0,31; 2,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,34</t>
+          <t>0,98; 3,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,94</t>
+          <t>0,84; 3,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,53</t>
+          <t>0,89; 3,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,08</t>
+          <t>0,79; 3,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,36</t>
+          <t>0,79; 2,32</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,76</t>
+          <t>0,55; 1,77</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,6</t>
+          <t>0,8; 2,7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,19</t>
+          <t>0,81; 2,1</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,73</t>
+          <t>0,71; 2,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,77</t>
+          <t>0,16; 1,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,7</t>
+          <t>1,17; 3,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,93</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,67</t>
+          <t>0,17; 1,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,57</t>
+          <t>0,16; 1,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,68</t>
+          <t>1,19; 3,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,1</t>
+          <t>0,1; 1,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,78</t>
+          <t>0,59; 1,7</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,25</t>
+          <t>0,27; 1,21</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,16</t>
+          <t>1,47; 3,08</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,81</t>
+          <t>0,13; 0,78</t>
         </is>
       </c>
     </row>
@@ -1837,57 +1837,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,56</t>
+          <t>0,76; 1,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,48</t>
+          <t>0,66; 1,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,73</t>
+          <t>0,77; 1,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,33</t>
+          <t>0,53; 1,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,57</t>
+          <t>0,79; 1,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,96</t>
+          <t>1,05; 1,93</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,83</t>
+          <t>0,96; 1,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,41</t>
+          <t>0,76; 1,4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,45</t>
+          <t>0,85; 1,43</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,52</t>
+          <t>0,97; 1,59</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,59</t>
+          <t>0,99; 1,59</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por tratamiento de las enfermedades de las encías</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por tratamiento de las enfermedades de las encías (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 7080</t>
+          <t>0; 6735</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1521; 10384</t>
+          <t>1745; 10250</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2896; 15033</t>
+          <t>2717; 13912</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>766; 27023</t>
+          <t>770; 24459</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5421</t>
+          <t>0; 5397</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4430; 17319</t>
+          <t>4283; 16988</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>942; 9692</t>
+          <t>942; 10373</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>506; 4320</t>
+          <t>502; 4741</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>930; 8230</t>
+          <t>934; 8076</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7400; 22508</t>
+          <t>8251; 22956</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4308; 17898</t>
+          <t>4876; 18308</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2368; 26003</t>
+          <t>2566; 23319</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2134; 14056</t>
+          <t>2070; 12710</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>987; 9418</t>
+          <t>982; 9876</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2032</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 8012</t>
+          <t>0; 9095</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2106; 12680</t>
+          <t>2826; 12471</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>980; 8972</t>
+          <t>986; 8029</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5561</t>
+          <t>0; 4944</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1705; 9403</t>
+          <t>1349; 9226</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6945; 20149</t>
+          <t>6125; 20299</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2283; 13707</t>
+          <t>2295; 12893</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 4924</t>
+          <t>0; 3985</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3010; 13598</t>
+          <t>2578; 13350</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6434</t>
+          <t>0; 6779</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1002; 8939</t>
+          <t>986; 9717</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4498</t>
+          <t>0; 4528</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1292; 10090</t>
+          <t>1211; 10231</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6768</t>
+          <t>0; 6764</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4061; 18335</t>
+          <t>4763; 20408</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5356</t>
+          <t>0; 5339</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2124; 8521</t>
+          <t>2149; 8593</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>939; 8581</t>
+          <t>949; 8671</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7054; 24470</t>
+          <t>7469; 23341</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 6813</t>
+          <t>0; 6245</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4436; 14807</t>
+          <t>4295; 14651</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>933; 10643</t>
+          <t>926; 10667</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 12863</t>
+          <t>0; 14420</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2011</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>711; 8205</t>
+          <t>553; 8553</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2104; 12749</t>
+          <t>2778; 13009</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>900; 8171</t>
+          <t>895; 8388</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2041; 12787</t>
+          <t>2041; 12030</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1194; 11758</t>
+          <t>1229; 10838</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5244; 17961</t>
+          <t>4981; 20222</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2410; 16028</t>
+          <t>1972; 15704</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2037; 12409</t>
+          <t>1962; 12012</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3044; 15994</t>
+          <t>3022; 14650</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1899</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1129; 9370</t>
+          <t>1099; 9675</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1921</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1224</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5068</t>
+          <t>0; 5677</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6333</t>
+          <t>0; 6035</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>823; 6686</t>
+          <t>816; 7015</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 8286</t>
+          <t>0; 7799</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5083</t>
+          <t>0; 5589</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2148; 13212</t>
+          <t>2145; 14152</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>836; 6864</t>
+          <t>823; 6864</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 7680</t>
+          <t>0; 7785</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4649</t>
+          <t>0; 4642</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>952; 8785</t>
+          <t>951; 7737</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>991; 11332</t>
+          <t>978; 11850</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1377; 10501</t>
+          <t>1533; 9882</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5789</t>
+          <t>0; 4634</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1018; 9840</t>
+          <t>1024; 10159</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5141</t>
+          <t>0; 4441</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1029; 6105</t>
+          <t>1070; 6276</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 6115</t>
+          <t>0; 5991</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2878; 13654</t>
+          <t>2997; 13884</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1989; 12403</t>
+          <t>1938; 11821</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3600; 14390</t>
+          <t>3603; 13843</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1437; 10347</t>
+          <t>947; 10614</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>892; 7769</t>
+          <t>0; 6708</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1056; 11655</t>
+          <t>1065; 13932</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1738; 11196</t>
+          <t>1875; 13031</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4539; 18034</t>
+          <t>5288; 17794</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4506; 18404</t>
+          <t>5241; 19486</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4443; 17177</t>
+          <t>4357; 16431</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>7122; 25519</t>
+          <t>6569; 25034</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7888; 23674</t>
+          <t>7921; 23289</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6848; 21195</t>
+          <t>6593; 21236</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7108; 24177</t>
+          <t>7451; 25081</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12126; 31227</t>
+          <t>11596; 29921</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3264; 14353</t>
+          <t>3718; 14337</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1058; 11244</t>
+          <t>1044; 10553</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7526; 23660</t>
+          <t>7476; 23497</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 8460</t>
+          <t>0; 9740</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1022; 9868</t>
+          <t>1011; 9228</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1104; 10981</t>
+          <t>1111; 12083</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8806; 25475</t>
+          <t>8246; 25129</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1093; 7767</t>
+          <t>712; 8130</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6128; 19932</t>
+          <t>6587; 19050</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4142; 16752</t>
+          <t>3621; 16154</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19750; 42073</t>
+          <t>19553; 41021</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2229; 13034</t>
+          <t>2169; 12551</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>18164; 38256</t>
+          <t>18548; 38698</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>20054; 43082</t>
+          <t>19176; 43009</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21809; 46014</t>
+          <t>20435; 45366</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16831; 44629</t>
+          <t>17637; 47547</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>21919; 43006</t>
+          <t>21592; 42782</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>33303; 61523</t>
+          <t>32881; 60713</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25919; 52492</t>
+          <t>27394; 51842</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>27131; 50506</t>
+          <t>27140; 49962</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>44581; 75159</t>
+          <t>43972; 74330</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>57445; 91903</t>
+          <t>58938; 96114</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>53556; 87748</t>
+          <t>54526; 88150</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>49680; 87707</t>
+          <t>50028; 88190</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C06-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C06-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,52</t>
+          <t>0,0; 3,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,09</t>
+          <t>0,65; 4,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,67</t>
+          <t>1,18; 5,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 8,01</t>
+          <t>0,23; 5,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 2,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,82</t>
+          <t>1,89; 6,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,21</t>
+          <t>0,38; 3,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,65</t>
+          <t>0,16; 1,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,06</t>
+          <t>0,23; 2,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,59</t>
+          <t>1,63; 4,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,72</t>
+          <t>1,04; 3,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,93</t>
+          <t>0,37; 2,64</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,1</t>
+          <t>0,51; 3,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,43</t>
+          <t>0,24; 2,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,83</t>
+          <t>0,47; 2,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,83</t>
+          <t>0,23; 1,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,84</t>
+          <t>0,33; 1,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,39</t>
+          <t>0,81; 2,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,53</t>
+          <t>0,35; 1,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,53</t>
+          <t>0,0; 0,68</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,32</t>
+          <t>0,27; 1,24</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,31</t>
+          <t>0,33; 3,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,4</t>
+          <t>0,3; 3,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 6,21</t>
+          <t>1,48; 5,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,56</t>
+          <t>0,58; 2,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,65</t>
+          <t>0,19; 1,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,75</t>
+          <t>1,15; 4,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,04</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,3</t>
+          <t>0,69; 2,32</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,99</t>
+          <t>0,35; 3,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,61</t>
+          <t>0,0; 4,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,76</t>
+          <t>0,16; 2,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,34</t>
+          <t>0,92; 4,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,45</t>
+          <t>0,26; 2,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,45</t>
+          <t>0,56; 3,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,29</t>
+          <t>0,35; 3,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,57</t>
+          <t>0,78; 3,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,39</t>
+          <t>0,31; 2,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,77</t>
+          <t>0,3; 1,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,87</t>
+          <t>0,41; 2,09</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,11%</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,04</t>
+          <t>0,58; 4,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1297,42 +1297,42 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,26</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,82</t>
+          <t>0,56; 4,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,66</t>
+          <t>0,49; 3,08</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,59</t>
+          <t>0,31; 2,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 0,53</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,09</t>
+          <t>0,38; 3,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,42; 5,07</t>
+          <t>0,69; 5,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,89</t>
+          <t>0,5; 3,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,84</t>
+          <t>0,37; 3,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,55</t>
+          <t>0,39; 2,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,7</t>
+          <t>0,57; 2,69</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,46</t>
+          <t>0,41; 2,54</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,77</t>
+          <t>0,71; 2,52</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,29</t>
+          <t>0,31; 2,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,16; 1,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,15</t>
+          <t>0,41; 2,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,17</t>
+          <t>0,29; 1,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,3</t>
+          <t>1,03; 3,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,11</t>
+          <t>0,7; 3,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,37</t>
+          <t>0,89; 3,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,02</t>
+          <t>1,64; 3,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,32</t>
+          <t>0,81; 2,45</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,77</t>
+          <t>0,54; 1,74</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,7</t>
+          <t>0,79; 2,66</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,1</t>
+          <t>1,09; 2,25</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,73</t>
+          <t>0,69; 2,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,66</t>
+          <t>0,16; 1,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,67</t>
+          <t>1,27; 3,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,14; 1,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,56</t>
+          <t>0,17; 1,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,72</t>
+          <t>0,16; 1,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,63</t>
+          <t>1,32; 3,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,15</t>
+          <t>0,1; 1,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,7</t>
+          <t>0,56; 1,76</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,21</t>
+          <t>0,32; 1,29</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,08</t>
+          <t>1,5; 3,13</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,78</t>
+          <t>0,17; 0,86</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,58</t>
+          <t>0,73; 1,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,48</t>
+          <t>0,66; 1,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,7</t>
+          <t>0,78; 1,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,42</t>
+          <t>0,49; 1,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,56</t>
+          <t>0,79; 1,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,93</t>
+          <t>1,03; 1,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,81</t>
+          <t>0,95; 1,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,4</t>
+          <t>0,86; 1,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,43</t>
+          <t>0,86; 1,46</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,59</t>
+          <t>0,95; 1,51</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,59</t>
+          <t>1,0; 1,63</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,27</t>
+          <t>0,75; 1,17</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>6033</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6735</t>
+          <t>0; 6815</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1745; 10250</t>
+          <t>1633; 10831</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2717; 13912</t>
+          <t>2895; 14252</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>770; 24459</t>
+          <t>689; 16737</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5397</t>
+          <t>0; 5378</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4283; 16988</t>
+          <t>4720; 17113</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>942; 10373</t>
+          <t>937; 8544</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>502; 4741</t>
+          <t>483; 4007</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>934; 8076</t>
+          <t>923; 8199</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8251; 22956</t>
+          <t>8157; 23953</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4876; 18308</t>
+          <t>5131; 18293</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2566; 23319</t>
+          <t>2241; 16137</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4178</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>6535</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2070; 12710</t>
+          <t>2079; 12404</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>982; 9876</t>
+          <t>979; 10317</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2432,47 +2432,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 9095</t>
+          <t>0; 7645</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2826; 12471</t>
+          <t>2092; 11832</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>986; 8029</t>
+          <t>986; 8035</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4944</t>
+          <t>0; 5094</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1349; 9226</t>
+          <t>1765; 8984</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6125; 20299</t>
+          <t>6908; 20358</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2295; 12893</t>
+          <t>2944; 13365</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 3985</t>
+          <t>0; 5138</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2578; 13350</t>
+          <t>2811; 13011</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>8227</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6779</t>
+          <t>0; 5891</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>986; 9717</t>
+          <t>972; 9010</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4528</t>
+          <t>0; 5397</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1211; 10231</t>
+          <t>887; 9646</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6764</t>
+          <t>0; 5848</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4763; 20408</t>
+          <t>4855; 19257</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5339</t>
+          <t>0; 5344</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2149; 8593</t>
+          <t>1986; 8727</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>949; 8671</t>
+          <t>982; 9680</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7469; 23341</t>
+          <t>7171; 25061</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 6245</t>
+          <t>0; 7337</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4295; 14651</t>
+          <t>4402; 14925</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>4503</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6838</t>
+          <t>7464</t>
         </is>
       </c>
     </row>
@@ -2833,12 +2833,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>926; 10667</t>
+          <t>924; 10379</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 14420</t>
+          <t>0; 12735</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2848,47 +2848,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>553; 8553</t>
+          <t>609; 9770</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2778; 13009</t>
+          <t>2764; 12638</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>895; 8388</t>
+          <t>895; 7652</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2041; 12030</t>
+          <t>1954; 11987</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1229; 10838</t>
+          <t>1455; 12586</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4981; 20222</t>
+          <t>4430; 17622</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1972; 15704</t>
+          <t>2050; 17339</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1962; 12012</t>
+          <t>2047; 12058</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3022; 14650</t>
+          <t>3244; 16482</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>432</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>432</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1099; 9675</t>
+          <t>1109; 9429</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3061,42 +3061,42 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5677</t>
+          <t>0; 6218</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6035</t>
+          <t>0; 6758</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>816; 7015</t>
+          <t>820; 6896</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 7799</t>
+          <t>0; 2158</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5589</t>
+          <t>0; 5122</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2145; 14152</t>
+          <t>1896; 11921</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>823; 6864</t>
+          <t>832; 6799</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 7785</t>
+          <t>0; 2169</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>6893</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4642</t>
+          <t>0; 4600</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>951; 7737</t>
+          <t>951; 7956</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>978; 11850</t>
+          <t>1611; 11859</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1533; 9882</t>
+          <t>1260; 9120</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4634</t>
+          <t>0; 5188</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1024; 10159</t>
+          <t>986; 8936</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4441</t>
+          <t>0; 5239</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1070; 6276</t>
+          <t>990; 6500</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 5991</t>
+          <t>0; 6141</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2997; 13884</t>
+          <t>2921; 13864</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1938; 11821</t>
+          <t>1991; 12220</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3603; 13843</t>
+          <t>3535; 12631</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>15806</t>
+          <t>18092</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>20895</t>
+          <t>23334</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>947; 10614</t>
+          <t>1448; 11001</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 6708</t>
+          <t>896; 8318</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1065; 13932</t>
+          <t>1833; 13186</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1875; 13031</t>
+          <t>1992; 11239</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5288; 17794</t>
+          <t>5569; 18903</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5241; 19486</t>
+          <t>4387; 18778</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4357; 16431</t>
+          <t>4334; 17243</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6569; 25034</t>
+          <t>12165; 25794</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7921; 23289</t>
+          <t>8146; 24554</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6593; 21236</t>
+          <t>6508; 20952</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7451; 25081</t>
+          <t>7363; 24759</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11596; 29921</t>
+          <t>15643; 32322</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>6898</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3718; 14337</t>
+          <t>3648; 14878</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1044; 10553</t>
+          <t>1039; 10692</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7476; 23497</t>
+          <t>8154; 25572</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 9740</t>
+          <t>1104; 9237</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1011; 9228</t>
+          <t>1014; 10262</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1111; 12083</t>
+          <t>1111; 10994</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8246; 25129</t>
+          <t>9131; 24239</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>712; 8130</t>
+          <t>771; 9055</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6587; 19050</t>
+          <t>6265; 19700</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3621; 16154</t>
+          <t>4288; 17181</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19553; 41021</t>
+          <t>19936; 41678</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2169; 12551</t>
+          <t>2674; 13574</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27826</t>
+          <t>26106</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>37773</t>
+          <t>39710</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>65599</t>
+          <t>65816</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>18548; 38698</t>
+          <t>17947; 39477</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>19176; 43009</t>
+          <t>19331; 42640</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20435; 45366</t>
+          <t>20681; 46112</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17637; 47547</t>
+          <t>16717; 38755</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>21592; 42782</t>
+          <t>21766; 43025</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32881; 60713</t>
+          <t>32266; 60387</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27394; 51842</t>
+          <t>27304; 51039</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>27140; 49962</t>
+          <t>31072; 51186</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>43972; 74330</t>
+          <t>44777; 75670</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>58938; 96114</t>
+          <t>57838; 91307</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>54526; 88150</t>
+          <t>55441; 89976</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>50028; 88190</t>
+          <t>52408; 82327</t>
         </is>
       </c>
     </row>
